--- a/notebooks/Random Forest/predictions_ele.xlsx
+++ b/notebooks/Random Forest/predictions_ele.xlsx
@@ -479,7 +479,7 @@
         <v>68.25</v>
       </c>
       <c r="D3" t="n">
-        <v>68.08643038600285</v>
+        <v>68.08643038600289</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>71.51000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>70.54224977633478</v>
+        <v>70.5422497763348</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>72.2</v>
       </c>
       <c r="D5" t="n">
-        <v>71.39897614718616</v>
+        <v>71.39897614718615</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         <v>71.62</v>
       </c>
       <c r="D8" t="n">
-        <v>70.56354864538238</v>
+        <v>70.56354864538241</v>
       </c>
     </row>
     <row r="9">
@@ -607,7 +607,7 @@
         <v>72.91</v>
       </c>
       <c r="D11" t="n">
-        <v>72.13483005673247</v>
+        <v>72.1348300567325</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>68.3</v>
       </c>
       <c r="D12" t="n">
-        <v>68.50094651695525</v>
+        <v>68.50094651695528</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>73.55</v>
       </c>
       <c r="D13" t="n">
-        <v>72.70783295634919</v>
+        <v>72.70783295634918</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>70.28152107142859</v>
+        <v>70.28152107142861</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>69.81999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>69.7810808488764</v>
+        <v>69.78108084887639</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>77.14</v>
       </c>
       <c r="D16" t="n">
-        <v>76.97517753968253</v>
+        <v>76.97517753968251</v>
       </c>
     </row>
     <row r="17">
@@ -735,7 +735,7 @@
         <v>70.43000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>69.9692292216117</v>
+        <v>69.96922922161167</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>76.25</v>
       </c>
       <c r="D20" t="n">
-        <v>76.24578879731381</v>
+        <v>76.24578879731382</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>70.29000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>69.87332084184986</v>
+        <v>69.87332084184985</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         <v>71.98999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>70.91499133297263</v>
+        <v>70.91499133297265</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         <v>71.31999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>70.34366051046177</v>
+        <v>70.3436605104618</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>69.57516104653682</v>
+        <v>69.57516104653679</v>
       </c>
     </row>
     <row r="27">
@@ -879,7 +879,7 @@
         <v>74.88</v>
       </c>
       <c r="D28" t="n">
-        <v>74.7669846780996</v>
+        <v>74.76698467809962</v>
       </c>
     </row>
     <row r="29">
@@ -927,7 +927,7 @@
         <v>74.48999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>74.38166690566374</v>
+        <v>74.38166690566372</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         <v>70.44</v>
       </c>
       <c r="D32" t="n">
-        <v>69.96380410256408</v>
+        <v>69.96380410256407</v>
       </c>
     </row>
     <row r="33">
@@ -975,7 +975,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>70.99946946428575</v>
+        <v>70.99946946428577</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v>70.43000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>69.93313459859583</v>
+        <v>69.93313459859581</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         <v>72.2</v>
       </c>
       <c r="D36" t="n">
-        <v>71.40979787698417</v>
+        <v>71.40979787698419</v>
       </c>
     </row>
     <row r="37">
@@ -1039,7 +1039,7 @@
         <v>71.12</v>
       </c>
       <c r="D38" t="n">
-        <v>70.33327114452797</v>
+        <v>70.333271144528</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         <v>71.65000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>70.53366755411257</v>
+        <v>70.5336675541126</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         <v>72.63</v>
       </c>
       <c r="D40" t="n">
-        <v>71.993973602244</v>
+        <v>71.99397360224398</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         <v>70.94</v>
       </c>
       <c r="D41" t="n">
-        <v>70.18138142230578</v>
+        <v>70.18138142230579</v>
       </c>
     </row>
     <row r="42">
@@ -1119,7 +1119,7 @@
         <v>70</v>
       </c>
       <c r="D43" t="n">
-        <v>69.83554622255782</v>
+        <v>69.83554622255784</v>
       </c>
     </row>
     <row r="44">
@@ -1167,7 +1167,7 @@
         <v>73.17</v>
       </c>
       <c r="D46" t="n">
-        <v>72.62738982142854</v>
+        <v>72.62738982142857</v>
       </c>
     </row>
     <row r="47">
@@ -1215,7 +1215,7 @@
         <v>79.2</v>
       </c>
       <c r="D49" t="n">
-        <v>78.47247692460317</v>
+        <v>78.47247692460316</v>
       </c>
     </row>
     <row r="50">
@@ -1247,7 +1247,7 @@
         <v>69.75</v>
       </c>
       <c r="D51" t="n">
-        <v>69.48407611549874</v>
+        <v>69.48407611549875</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         <v>70.43000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>69.96897201923075</v>
+        <v>69.96897201923073</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         <v>72.76000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>72.01289339120503</v>
+        <v>72.01289339120504</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         <v>72.04000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>70.95979224567105</v>
+        <v>70.95979224567104</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         <v>73.78</v>
       </c>
       <c r="D55" t="n">
-        <v>73.29899968253967</v>
+        <v>73.29899968253966</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         <v>67.17</v>
       </c>
       <c r="D56" t="n">
-        <v>67.27215010461755</v>
+        <v>67.27215010461757</v>
       </c>
     </row>
     <row r="57">
@@ -1375,7 +1375,7 @@
         <v>66.59</v>
       </c>
       <c r="D59" t="n">
-        <v>66.80938938492059</v>
+        <v>66.80938938492062</v>
       </c>
     </row>
     <row r="60">
@@ -1423,7 +1423,7 @@
         <v>73.19</v>
       </c>
       <c r="D62" t="n">
-        <v>72.59319849206345</v>
+        <v>72.59319849206349</v>
       </c>
     </row>
     <row r="63">
@@ -1455,7 +1455,7 @@
         <v>73.27</v>
       </c>
       <c r="D64" t="n">
-        <v>72.68535815476187</v>
+        <v>72.6853581547619</v>
       </c>
     </row>
     <row r="65">
@@ -1487,7 +1487,7 @@
         <v>71.84</v>
       </c>
       <c r="D66" t="n">
-        <v>70.85037538059164</v>
+        <v>70.85037538059166</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         <v>71.47</v>
       </c>
       <c r="D67" t="n">
-        <v>70.52399041125544</v>
+        <v>70.52399041125547</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         <v>74.86</v>
       </c>
       <c r="D68" t="n">
-        <v>74.85829465825836</v>
+        <v>74.85829465825837</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         <v>72.87</v>
       </c>
       <c r="D69" t="n">
-        <v>72.02003355173895</v>
+        <v>72.02003355173893</v>
       </c>
     </row>
     <row r="70">
@@ -1583,7 +1583,7 @@
         <v>72.15000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>71.35189353535355</v>
+        <v>71.35189353535357</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         <v>75.44</v>
       </c>
       <c r="D73" t="n">
-        <v>75.51926762112878</v>
+        <v>75.51926762112876</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         <v>72.34</v>
       </c>
       <c r="D74" t="n">
-        <v>71.63286970238097</v>
+        <v>71.63286970238099</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         <v>72.04000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>70.93667387265515</v>
+        <v>70.93667387265518</v>
       </c>
     </row>
     <row r="76">
@@ -1663,7 +1663,7 @@
         <v>76.31999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>76.32901453144078</v>
+        <v>76.32901453144081</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         <v>72.43000000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>71.87497668109668</v>
+        <v>71.8749766810967</v>
       </c>
     </row>
     <row r="79">
@@ -1711,7 +1711,7 @@
         <v>73.06999999999999</v>
       </c>
       <c r="D80" t="n">
-        <v>72.31398700396822</v>
+        <v>72.31398700396824</v>
       </c>
     </row>
     <row r="81">
@@ -1775,7 +1775,7 @@
         <v>79.38</v>
       </c>
       <c r="D84" t="n">
-        <v>78.22840503968251</v>
+        <v>78.2284050396825</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         <v>76.55</v>
       </c>
       <c r="D85" t="n">
-        <v>76.49568935078811</v>
+        <v>76.49568935078813</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         <v>76.11</v>
       </c>
       <c r="D86" t="n">
-        <v>76.02851451159951</v>
+        <v>76.02851451159952</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/Random Forest/predictions_ele.xlsx
+++ b/notebooks/Random Forest/predictions_ele.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ</t>
+          <t>ОПЖ_прогноз</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>predictions</t>
+          <t>ОПЖ_реальный</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_абсолютная</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_относительная_%</t>
         </is>
       </c>
     </row>
@@ -457,13 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="n">
+        <v>69.17232314228117</v>
+      </c>
+      <c r="D2" t="n">
         <v>70.77</v>
       </c>
-      <c r="D2" t="n">
-        <v>70.06791937865498</v>
+      <c r="E2" t="n">
+        <v>1.597676857718824</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.257562325446975</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="n">
+        <v>67.68987071428569</v>
+      </c>
+      <c r="D3" t="n">
         <v>68.25</v>
       </c>
-      <c r="D3" t="n">
-        <v>68.08643038600289</v>
+      <c r="E3" t="n">
+        <v>0.5601292857143108</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8207022501308583</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="n">
+        <v>69.96289246693608</v>
+      </c>
+      <c r="D4" t="n">
         <v>71.51000000000001</v>
       </c>
-      <c r="D4" t="n">
-        <v>70.5422497763348</v>
+      <c r="E4" t="n">
+        <v>1.547107533063922</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.163484174330754</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="n">
+        <v>70.96531310372275</v>
+      </c>
+      <c r="D5" t="n">
         <v>72.2</v>
       </c>
-      <c r="D5" t="n">
-        <v>71.39897614718615</v>
+      <c r="E5" t="n">
+        <v>1.234686896277253</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.710092654123619</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="n">
+        <v>71.92871794075552</v>
+      </c>
+      <c r="D6" t="n">
         <v>73.7</v>
       </c>
-      <c r="D6" t="n">
-        <v>72.96664805555554</v>
+      <c r="E6" t="n">
+        <v>1.771282059244484</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.403367787305949</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="n">
+        <v>70.12599540012437</v>
+      </c>
+      <c r="D7" t="n">
         <v>71.98</v>
       </c>
-      <c r="D7" t="n">
-        <v>70.92661077741707</v>
+      <c r="E7" t="n">
+        <v>1.854004599875637</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.575721867012555</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="n">
+        <v>69.87102815611038</v>
+      </c>
+      <c r="D8" t="n">
         <v>71.62</v>
       </c>
-      <c r="D8" t="n">
-        <v>70.56354864538241</v>
+      <c r="E8" t="n">
+        <v>1.74897184388962</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.442015978622759</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="n">
+        <v>71.94929920400561</v>
+      </c>
+      <c r="D9" t="n">
         <v>73.69</v>
       </c>
-      <c r="D9" t="n">
-        <v>72.99912950396822</v>
+      <c r="E9" t="n">
+        <v>1.740700795994385</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.362194050745536</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="n">
+        <v>70.58450929117815</v>
+      </c>
+      <c r="D10" t="n">
         <v>71.7</v>
       </c>
-      <c r="D10" t="n">
-        <v>70.60835704184707</v>
+      <c r="E10" t="n">
+        <v>1.115490708821852</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.555775047171342</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="n">
+        <v>71.39871919260817</v>
+      </c>
+      <c r="D11" t="n">
         <v>72.91</v>
       </c>
-      <c r="D11" t="n">
-        <v>72.1348300567325</v>
+      <c r="E11" t="n">
+        <v>1.511280807391827</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.072803192143502</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="n">
+        <v>67.59391075396826</v>
+      </c>
+      <c r="D12" t="n">
         <v>68.3</v>
       </c>
-      <c r="D12" t="n">
-        <v>68.50094651695528</v>
+      <c r="E12" t="n">
+        <v>0.7060892460317376</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.033805631085999</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="n">
+        <v>71.6683741537459</v>
+      </c>
+      <c r="D13" t="n">
         <v>73.55</v>
       </c>
-      <c r="D13" t="n">
-        <v>72.70783295634918</v>
+      <c r="E13" t="n">
+        <v>1.881625846254096</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.558294828353632</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="n">
+        <v>69.71524198578736</v>
+      </c>
+      <c r="D14" t="n">
         <v>71.18000000000001</v>
       </c>
-      <c r="D14" t="n">
-        <v>70.28152107142861</v>
+      <c r="E14" t="n">
+        <v>1.464758014212649</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.057822441995854</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="n">
+        <v>68.6512482691806</v>
+      </c>
+      <c r="D15" t="n">
         <v>69.81999999999999</v>
       </c>
-      <c r="D15" t="n">
-        <v>69.78108084887639</v>
+      <c r="E15" t="n">
+        <v>1.168751730819395</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.673949772012883</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="n">
+        <v>74.07435671621003</v>
+      </c>
+      <c r="D16" t="n">
         <v>77.14</v>
       </c>
-      <c r="D16" t="n">
-        <v>76.97517753968251</v>
+      <c r="E16" t="n">
+        <v>3.065643283789967</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.974129224513828</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="n">
+        <v>72.03742688593468</v>
+      </c>
+      <c r="D17" t="n">
         <v>73.70999999999999</v>
       </c>
-      <c r="D17" t="n">
-        <v>73.00841174603173</v>
+      <c r="E17" t="n">
+        <v>1.672573114065315</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.269126460541738</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C18" t="n">
+        <v>71.58717492090706</v>
+      </c>
+      <c r="D18" t="n">
         <v>73.08</v>
       </c>
-      <c r="D18" t="n">
-        <v>72.3660474801587</v>
+      <c r="E18" t="n">
+        <v>1.492825079092938</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.042727256558481</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="n">
+        <v>68.25276882936508</v>
+      </c>
+      <c r="D19" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="D19" t="n">
-        <v>69.96922922161167</v>
+      <c r="E19" t="n">
+        <v>2.177231170634926</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.091340580200093</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C20" t="n">
+        <v>73.97054796468383</v>
+      </c>
+      <c r="D20" t="n">
         <v>76.25</v>
       </c>
-      <c r="D20" t="n">
-        <v>76.24578879731382</v>
+      <c r="E20" t="n">
+        <v>2.279452035316169</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.989445292217926</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C21" t="n">
+        <v>68.85492275014022</v>
+      </c>
+      <c r="D21" t="n">
         <v>70.29000000000001</v>
       </c>
-      <c r="D21" t="n">
-        <v>69.87332084184985</v>
+      <c r="E21" t="n">
+        <v>1.435077249859788</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.041652084023029</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C22" t="n">
+        <v>70.19277824520144</v>
+      </c>
+      <c r="D22" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="D22" t="n">
-        <v>70.91499133297265</v>
+      <c r="E22" t="n">
+        <v>1.797221754798557</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.496488060561962</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C23" t="n">
+        <v>69.10623318880535</v>
+      </c>
+      <c r="D23" t="n">
         <v>71.05</v>
       </c>
-      <c r="D23" t="n">
-        <v>70.23505556913121</v>
+      <c r="E23" t="n">
+        <v>1.943766811194649</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.735773133278887</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C24" t="n">
+        <v>72.03225486386093</v>
+      </c>
+      <c r="D24" t="n">
         <v>73.70999999999999</v>
       </c>
-      <c r="D24" t="n">
-        <v>73.00384263888887</v>
+      <c r="E24" t="n">
+        <v>1.677745136139066</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.276143177505177</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C25" t="n">
+        <v>69.68945542232727</v>
+      </c>
+      <c r="D25" t="n">
         <v>71.31999999999999</v>
       </c>
-      <c r="D25" t="n">
-        <v>70.3436605104618</v>
+      <c r="E25" t="n">
+        <v>1.630544577672723</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.286237489726196</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C26" t="n">
+        <v>68.98858510400166</v>
+      </c>
+      <c r="D26" t="n">
         <v>69.79000000000001</v>
       </c>
-      <c r="D26" t="n">
-        <v>69.57516104653679</v>
+      <c r="E26" t="n">
+        <v>0.8014148959983487</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.148323393033885</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C27" t="n">
+        <v>70.44914945844457</v>
+      </c>
+      <c r="D27" t="n">
         <v>72.45</v>
       </c>
-      <c r="D27" t="n">
-        <v>71.86359432539685</v>
+      <c r="E27" t="n">
+        <v>2.000850541555437</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.761698470055813</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C28" t="n">
+        <v>72.16903376946308</v>
+      </c>
+      <c r="D28" t="n">
         <v>74.88</v>
       </c>
-      <c r="D28" t="n">
-        <v>74.76698467809962</v>
+      <c r="E28" t="n">
+        <v>2.710966230536911</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.620414303601645</v>
       </c>
     </row>
     <row r="29">
@@ -889,13 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C29" t="n">
+        <v>71.00473513084108</v>
+      </c>
+      <c r="D29" t="n">
         <v>72.44</v>
       </c>
-      <c r="D29" t="n">
-        <v>71.87154396825399</v>
+      <c r="E29" t="n">
+        <v>1.435264869158914</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.981315390887512</v>
       </c>
     </row>
     <row r="30">
@@ -905,13 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>67.95405593975467</v>
+      </c>
+      <c r="D30" t="n">
         <v>69.3</v>
       </c>
-      <c r="D30" t="n">
-        <v>68.80912606782108</v>
+      <c r="E30" t="n">
+        <v>1.34594406024533</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.942199221133232</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +1105,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C31" t="n">
+        <v>73.04849061617819</v>
+      </c>
+      <c r="D31" t="n">
         <v>74.48999999999999</v>
       </c>
-      <c r="D31" t="n">
-        <v>74.38166690566372</v>
+      <c r="E31" t="n">
+        <v>1.44150938382181</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.935171679180843</v>
       </c>
     </row>
     <row r="32">
@@ -937,13 +1127,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C32" t="n">
+        <v>69.15347442786381</v>
+      </c>
+      <c r="D32" t="n">
         <v>70.44</v>
       </c>
-      <c r="D32" t="n">
-        <v>69.96380410256407</v>
+      <c r="E32" t="n">
+        <v>1.286525572136185</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.826413361919627</v>
       </c>
     </row>
     <row r="33">
@@ -953,13 +1149,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C33" t="n">
+        <v>69.60200610389614</v>
+      </c>
+      <c r="D33" t="n">
         <v>70.67</v>
       </c>
-      <c r="D33" t="n">
-        <v>69.95911630494503</v>
+      <c r="E33" t="n">
+        <v>1.067993896103857</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.511240832183186</v>
       </c>
     </row>
     <row r="34">
@@ -969,13 +1171,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C34" t="n">
+        <v>70.56750871931354</v>
+      </c>
+      <c r="D34" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="D34" t="n">
-        <v>70.99946946428577</v>
+      <c r="E34" t="n">
+        <v>1.532491280686457</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.125508017595641</v>
       </c>
     </row>
     <row r="35">
@@ -985,13 +1193,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C35" t="n">
+        <v>69.37082216205218</v>
+      </c>
+      <c r="D35" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="D35" t="n">
-        <v>69.93313459859581</v>
+      <c r="E35" t="n">
+        <v>1.059177837947828</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.503873119335267</v>
       </c>
     </row>
     <row r="36">
@@ -1001,13 +1215,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C36" t="n">
+        <v>70.63271741794561</v>
+      </c>
+      <c r="D36" t="n">
         <v>72.2</v>
       </c>
-      <c r="D36" t="n">
-        <v>71.40979787698419</v>
+      <c r="E36" t="n">
+        <v>1.567282582054389</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.17075149869029</v>
       </c>
     </row>
     <row r="37">
@@ -1017,13 +1237,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C37" t="n">
+        <v>70.62667419691363</v>
+      </c>
+      <c r="D37" t="n">
         <v>71.83</v>
       </c>
-      <c r="D37" t="n">
-        <v>70.87067657106785</v>
+      <c r="E37" t="n">
+        <v>1.203325803086372</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.675241268392555</v>
       </c>
     </row>
     <row r="38">
@@ -1033,13 +1259,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C38" t="n">
+        <v>70.179268170627</v>
+      </c>
+      <c r="D38" t="n">
         <v>71.12</v>
       </c>
-      <c r="D38" t="n">
-        <v>70.333271144528</v>
+      <c r="E38" t="n">
+        <v>0.9407318293730071</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.322738792706703</v>
       </c>
     </row>
     <row r="39">
@@ -1049,13 +1281,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C39" t="n">
+        <v>69.81433937512183</v>
+      </c>
+      <c r="D39" t="n">
         <v>71.65000000000001</v>
       </c>
-      <c r="D39" t="n">
-        <v>70.5336675541126</v>
+      <c r="E39" t="n">
+        <v>1.835660624878173</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.56198272837149</v>
       </c>
     </row>
     <row r="40">
@@ -1065,13 +1303,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C40" t="n">
+        <v>70.9657091239547</v>
+      </c>
+      <c r="D40" t="n">
         <v>72.63</v>
       </c>
-      <c r="D40" t="n">
-        <v>71.99397360224398</v>
+      <c r="E40" t="n">
+        <v>1.6642908760453</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.291464788717196</v>
       </c>
     </row>
     <row r="41">
@@ -1081,13 +1325,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C41" t="n">
+        <v>69.95279562614991</v>
+      </c>
+      <c r="D41" t="n">
         <v>70.94</v>
       </c>
-      <c r="D41" t="n">
-        <v>70.18138142230579</v>
+      <c r="E41" t="n">
+        <v>0.9872043738500906</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.391604699534946</v>
       </c>
     </row>
     <row r="42">
@@ -1097,13 +1347,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C42" t="n">
+        <v>68.86773337070231</v>
+      </c>
+      <c r="D42" t="n">
         <v>70.06</v>
       </c>
-      <c r="D42" t="n">
-        <v>69.90624534181097</v>
+      <c r="E42" t="n">
+        <v>1.192266629297691</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.701779373819142</v>
       </c>
     </row>
     <row r="43">
@@ -1113,13 +1369,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C43" t="n">
+        <v>68.42300308527825</v>
+      </c>
+      <c r="D43" t="n">
         <v>70</v>
       </c>
-      <c r="D43" t="n">
-        <v>69.83554622255784</v>
+      <c r="E43" t="n">
+        <v>1.576996914721747</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.252852735316781</v>
       </c>
     </row>
     <row r="44">
@@ -1129,13 +1391,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C44" t="n">
+        <v>72.62463454567525</v>
+      </c>
+      <c r="D44" t="n">
         <v>75.36</v>
       </c>
-      <c r="D44" t="n">
-        <v>75.39947589133078</v>
+      <c r="E44" t="n">
+        <v>2.73536545432475</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.629731229199509</v>
       </c>
     </row>
     <row r="45">
@@ -1145,13 +1413,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C45" t="n">
+        <v>67.95536009920632</v>
+      </c>
+      <c r="D45" t="n">
         <v>69.39</v>
       </c>
-      <c r="D45" t="n">
-        <v>68.9933350757576</v>
+      <c r="E45" t="n">
+        <v>1.434639900793684</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.067502379008047</v>
       </c>
     </row>
     <row r="46">
@@ -1161,13 +1435,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C46" t="n">
+        <v>71.89987128651828</v>
+      </c>
+      <c r="D46" t="n">
         <v>73.17</v>
       </c>
-      <c r="D46" t="n">
-        <v>72.62738982142857</v>
+      <c r="E46" t="n">
+        <v>1.270128713481725</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.735859933691028</v>
       </c>
     </row>
     <row r="47">
@@ -1177,13 +1457,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C47" t="n">
+        <v>68.73233173425282</v>
+      </c>
+      <c r="D47" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="D47" t="n">
-        <v>69.29835877831107</v>
+      <c r="E47" t="n">
+        <v>0.8076682657471821</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.161444155517949</v>
       </c>
     </row>
     <row r="48">
@@ -1193,13 +1479,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C48" t="n">
+        <v>76.12975604437233</v>
+      </c>
+      <c r="D48" t="n">
         <v>79.87</v>
       </c>
-      <c r="D48" t="n">
-        <v>78.30569299603171</v>
+      <c r="E48" t="n">
+        <v>3.740243955627676</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4.682914680891042</v>
       </c>
     </row>
     <row r="49">
@@ -1209,13 +1501,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C49" t="n">
+        <v>76.08253135642138</v>
+      </c>
+      <c r="D49" t="n">
         <v>79.2</v>
       </c>
-      <c r="D49" t="n">
-        <v>78.47247692460316</v>
+      <c r="E49" t="n">
+        <v>3.117468643578619</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.936197782296235</v>
       </c>
     </row>
     <row r="50">
@@ -1225,13 +1523,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C50" t="n">
+        <v>72.32298456643991</v>
+      </c>
+      <c r="D50" t="n">
         <v>74.53</v>
       </c>
-      <c r="D50" t="n">
-        <v>74.39055444444442</v>
+      <c r="E50" t="n">
+        <v>2.207015433560088</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.961244376170787</v>
       </c>
     </row>
     <row r="51">
@@ -1241,13 +1545,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C51" t="n">
+        <v>68.04971442005458</v>
+      </c>
+      <c r="D51" t="n">
         <v>69.75</v>
       </c>
-      <c r="D51" t="n">
-        <v>69.48407611549875</v>
+      <c r="E51" t="n">
+        <v>1.700285579945415</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.437685419276581</v>
       </c>
     </row>
     <row r="52">
@@ -1257,13 +1567,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C52" t="n">
+        <v>69.08796616692338</v>
+      </c>
+      <c r="D52" t="n">
         <v>70.43000000000001</v>
       </c>
-      <c r="D52" t="n">
-        <v>69.96897201923073</v>
+      <c r="E52" t="n">
+        <v>1.342033833076627</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.905486061446297</v>
       </c>
     </row>
     <row r="53">
@@ -1273,13 +1589,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C53" t="n">
+        <v>71.10719152568714</v>
+      </c>
+      <c r="D53" t="n">
         <v>72.76000000000001</v>
       </c>
-      <c r="D53" t="n">
-        <v>72.01289339120504</v>
+      <c r="E53" t="n">
+        <v>1.652808474312863</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.271589436933566</v>
       </c>
     </row>
     <row r="54">
@@ -1289,13 +1611,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C54" t="n">
+        <v>71.04943585292639</v>
+      </c>
+      <c r="D54" t="n">
         <v>72.04000000000001</v>
       </c>
-      <c r="D54" t="n">
-        <v>70.95979224567104</v>
+      <c r="E54" t="n">
+        <v>0.9905641470736128</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.37501963780346</v>
       </c>
     </row>
     <row r="55">
@@ -1305,13 +1633,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C55" t="n">
+        <v>71.97474265320916</v>
+      </c>
+      <c r="D55" t="n">
         <v>73.78</v>
       </c>
-      <c r="D55" t="n">
-        <v>73.29899968253966</v>
+      <c r="E55" t="n">
+        <v>1.805257346790839</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.446811258865328</v>
       </c>
     </row>
     <row r="56">
@@ -1321,13 +1655,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C56" t="n">
+        <v>67.64078525793647</v>
+      </c>
+      <c r="D56" t="n">
         <v>67.17</v>
       </c>
-      <c r="D56" t="n">
-        <v>67.27215010461757</v>
+      <c r="E56" t="n">
+        <v>-0.4707852579364697</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.7008861961239686</v>
       </c>
     </row>
     <row r="57">
@@ -1337,13 +1677,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C57" t="n">
+        <v>73.40096261211971</v>
+      </c>
+      <c r="D57" t="n">
         <v>76.16</v>
       </c>
-      <c r="D57" t="n">
-        <v>76.05781855921855</v>
+      <c r="E57" t="n">
+        <v>2.759037387880284</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.622685645851213</v>
       </c>
     </row>
     <row r="58">
@@ -1353,13 +1699,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C58" t="n">
+        <v>73.50760974293381</v>
+      </c>
+      <c r="D58" t="n">
         <v>75.25</v>
       </c>
-      <c r="D58" t="n">
-        <v>74.67610972943714</v>
+      <c r="E58" t="n">
+        <v>1.742390257066191</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.315468780154406</v>
       </c>
     </row>
     <row r="59">
@@ -1369,13 +1721,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C59" t="n">
+        <v>67.55989704260655</v>
+      </c>
+      <c r="D59" t="n">
         <v>66.59</v>
       </c>
-      <c r="D59" t="n">
-        <v>66.80938938492062</v>
+      <c r="E59" t="n">
+        <v>-0.9698970426065472</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-1.456520562556761</v>
       </c>
     </row>
     <row r="60">
@@ -1385,13 +1743,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C60" t="n">
+        <v>69.69305747297544</v>
+      </c>
+      <c r="D60" t="n">
         <v>70.68000000000001</v>
       </c>
-      <c r="D60" t="n">
-        <v>70.0357409550172</v>
+      <c r="E60" t="n">
+        <v>0.9869425270245671</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.396353320634645</v>
       </c>
     </row>
     <row r="61">
@@ -1401,13 +1765,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C61" t="n">
+        <v>71.11260269390412</v>
+      </c>
+      <c r="D61" t="n">
         <v>73.48</v>
       </c>
-      <c r="D61" t="n">
-        <v>72.67428055555553</v>
+      <c r="E61" t="n">
+        <v>2.367397306095882</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.221825402961188</v>
       </c>
     </row>
     <row r="62">
@@ -1417,13 +1787,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C62" t="n">
+        <v>70.83454384635556</v>
+      </c>
+      <c r="D62" t="n">
         <v>73.19</v>
       </c>
-      <c r="D62" t="n">
-        <v>72.59319849206349</v>
+      <c r="E62" t="n">
+        <v>2.35545615364444</v>
+      </c>
+      <c r="F62" t="n">
+        <v>3.218275930652329</v>
       </c>
     </row>
     <row r="63">
@@ -1433,13 +1809,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C63" t="n">
+        <v>71.07657343681771</v>
+      </c>
+      <c r="D63" t="n">
         <v>72.53</v>
       </c>
-      <c r="D63" t="n">
-        <v>71.96652597057013</v>
+      <c r="E63" t="n">
+        <v>1.45342656318229</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.003897095246506</v>
       </c>
     </row>
     <row r="64">
@@ -1449,13 +1831,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C64" t="n">
+        <v>71.58789735668948</v>
+      </c>
+      <c r="D64" t="n">
         <v>73.27</v>
       </c>
-      <c r="D64" t="n">
-        <v>72.6853581547619</v>
+      <c r="E64" t="n">
+        <v>1.682102643310515</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.295759032769912</v>
       </c>
     </row>
     <row r="65">
@@ -1465,13 +1853,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C65" t="n">
+        <v>69.52727075236972</v>
+      </c>
+      <c r="D65" t="n">
         <v>70.22</v>
       </c>
-      <c r="D65" t="n">
-        <v>69.83715970576596</v>
+      <c r="E65" t="n">
+        <v>0.6927292476302824</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.9865127422818035</v>
       </c>
     </row>
     <row r="66">
@@ -1481,13 +1875,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C66" t="n">
+        <v>70.4249294369823</v>
+      </c>
+      <c r="D66" t="n">
         <v>71.84</v>
       </c>
-      <c r="D66" t="n">
-        <v>70.85037538059166</v>
+      <c r="E66" t="n">
+        <v>1.415070563017707</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.969753010882109</v>
       </c>
     </row>
     <row r="67">
@@ -1497,13 +1897,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C67" t="n">
+        <v>69.34808430964475</v>
+      </c>
+      <c r="D67" t="n">
         <v>71.47</v>
       </c>
-      <c r="D67" t="n">
-        <v>70.52399041125547</v>
+      <c r="E67" t="n">
+        <v>2.121915690355252</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.968959969714918</v>
       </c>
     </row>
     <row r="68">
@@ -1513,13 +1919,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C68" t="n">
+        <v>73.09614713172181</v>
+      </c>
+      <c r="D68" t="n">
         <v>74.86</v>
       </c>
-      <c r="D68" t="n">
-        <v>74.85829465825837</v>
+      <c r="E68" t="n">
+        <v>1.763852868278192</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2.356202068231622</v>
       </c>
     </row>
     <row r="69">
@@ -1529,13 +1941,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C69" t="n">
+        <v>70.83936175941655</v>
+      </c>
+      <c r="D69" t="n">
         <v>72.87</v>
       </c>
-      <c r="D69" t="n">
-        <v>72.02003355173893</v>
+      <c r="E69" t="n">
+        <v>2.030638240583457</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.786658762979905</v>
       </c>
     </row>
     <row r="70">
@@ -1545,13 +1963,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C70" t="n">
+        <v>69.06594956744388</v>
+      </c>
+      <c r="D70" t="n">
         <v>70.61</v>
       </c>
-      <c r="D70" t="n">
-        <v>69.98605899614273</v>
+      <c r="E70" t="n">
+        <v>1.544050432556119</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.186730537538761</v>
       </c>
     </row>
     <row r="71">
@@ -1561,13 +1985,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C71" t="n">
+        <v>71.50300814140732</v>
+      </c>
+      <c r="D71" t="n">
         <v>73.05</v>
       </c>
-      <c r="D71" t="n">
-        <v>72.30059724206347</v>
+      <c r="E71" t="n">
+        <v>1.546991858592676</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.117716438867455</v>
       </c>
     </row>
     <row r="72">
@@ -1577,13 +2007,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C72" t="n">
+        <v>70.7638889704811</v>
+      </c>
+      <c r="D72" t="n">
         <v>72.15000000000001</v>
       </c>
-      <c r="D72" t="n">
-        <v>71.35189353535357</v>
+      <c r="E72" t="n">
+        <v>1.386111029518901</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.921151808065004</v>
       </c>
     </row>
     <row r="73">
@@ -1593,13 +2029,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C73" t="n">
+        <v>73.32648526507093</v>
+      </c>
+      <c r="D73" t="n">
         <v>75.44</v>
       </c>
-      <c r="D73" t="n">
-        <v>75.51926762112876</v>
+      <c r="E73" t="n">
+        <v>2.113514734929069</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.801583688930367</v>
       </c>
     </row>
     <row r="74">
@@ -1609,13 +2051,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C74" t="n">
+        <v>71.05648477279152</v>
+      </c>
+      <c r="D74" t="n">
         <v>72.34</v>
       </c>
-      <c r="D74" t="n">
-        <v>71.63286970238099</v>
+      <c r="E74" t="n">
+        <v>1.283515227208483</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.774281486326352</v>
       </c>
     </row>
     <row r="75">
@@ -1625,13 +2073,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C75" t="n">
+        <v>70.59074563227453</v>
+      </c>
+      <c r="D75" t="n">
         <v>72.04000000000001</v>
       </c>
-      <c r="D75" t="n">
-        <v>70.93667387265518</v>
+      <c r="E75" t="n">
+        <v>1.449254367725473</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.01173565758672</v>
       </c>
     </row>
     <row r="76">
@@ -1641,13 +2095,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C76" t="n">
+        <v>69.15053701492062</v>
+      </c>
+      <c r="D76" t="n">
         <v>70.33</v>
       </c>
-      <c r="D76" t="n">
-        <v>69.85965619548011</v>
+      <c r="E76" t="n">
+        <v>1.179462985079383</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.677041070779728</v>
       </c>
     </row>
     <row r="77">
@@ -1657,13 +2117,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="n">
+        <v>73.65490788321668</v>
+      </c>
+      <c r="D77" t="n">
         <v>76.31999999999999</v>
       </c>
-      <c r="D77" t="n">
-        <v>76.32901453144081</v>
+      <c r="E77" t="n">
+        <v>2.665092116783313</v>
+      </c>
+      <c r="F77" t="n">
+        <v>3.491997008363881</v>
       </c>
     </row>
     <row r="78">
@@ -1673,13 +2139,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C78" t="n">
+        <v>71.50372093530042</v>
+      </c>
+      <c r="D78" t="n">
         <v>72.43000000000001</v>
       </c>
-      <c r="D78" t="n">
-        <v>71.8749766810967</v>
+      <c r="E78" t="n">
+        <v>0.9262790646995853</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.278861058538707</v>
       </c>
     </row>
     <row r="79">
@@ -1689,13 +2161,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C79" t="n">
+        <v>73.66757800352428</v>
+      </c>
+      <c r="D79" t="n">
         <v>76.26000000000001</v>
       </c>
-      <c r="D79" t="n">
-        <v>76.20309568223445</v>
+      <c r="E79" t="n">
+        <v>2.592421996475721</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.399451870542515</v>
       </c>
     </row>
     <row r="80">
@@ -1705,13 +2183,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C80" t="n">
+        <v>71.64750904749665</v>
+      </c>
+      <c r="D80" t="n">
         <v>73.06999999999999</v>
       </c>
-      <c r="D80" t="n">
-        <v>72.31398700396824</v>
+      <c r="E80" t="n">
+        <v>1.422490952503338</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.946750995625206</v>
       </c>
     </row>
     <row r="81">
@@ -1721,13 +2205,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C81" t="n">
+        <v>65.4086848881674</v>
+      </c>
+      <c r="D81" t="n">
         <v>66.56</v>
       </c>
-      <c r="D81" t="n">
-        <v>65.7572507593795</v>
+      <c r="E81" t="n">
+        <v>1.151315111832602</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.729740252152347</v>
       </c>
     </row>
     <row r="82">
@@ -1737,13 +2227,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C82" t="n">
+        <v>73.52047434568803</v>
+      </c>
+      <c r="D82" t="n">
         <v>75.3</v>
       </c>
-      <c r="D82" t="n">
-        <v>74.82667265873006</v>
+      <c r="E82" t="n">
+        <v>1.779525654311968</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.363247880892387</v>
       </c>
     </row>
     <row r="83">
@@ -1753,13 +2249,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C83" t="n">
+        <v>70.45742291884615</v>
+      </c>
+      <c r="D83" t="n">
         <v>71.98999999999999</v>
       </c>
-      <c r="D83" t="n">
-        <v>70.94265561868693</v>
+      <c r="E83" t="n">
+        <v>1.532577081153846</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.128874956457628</v>
       </c>
     </row>
     <row r="84">
@@ -1769,13 +2271,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C84" t="n">
+        <v>75.76468267857145</v>
+      </c>
+      <c r="D84" t="n">
         <v>79.38</v>
       </c>
-      <c r="D84" t="n">
-        <v>78.2284050396825</v>
+      <c r="E84" t="n">
+        <v>3.615317321428549</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.554443589605127</v>
       </c>
     </row>
     <row r="85">
@@ -1785,13 +2293,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C85" t="n">
+        <v>74.46910123588158</v>
+      </c>
+      <c r="D85" t="n">
         <v>76.55</v>
       </c>
-      <c r="D85" t="n">
-        <v>76.49568935078813</v>
+      <c r="E85" t="n">
+        <v>2.080898764118416</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.718352402506095</v>
       </c>
     </row>
     <row r="86">
@@ -1801,13 +2315,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C86" t="n">
+        <v>73.25448565828881</v>
+      </c>
+      <c r="D86" t="n">
         <v>76.11</v>
       </c>
-      <c r="D86" t="n">
-        <v>76.02851451159952</v>
+      <c r="E86" t="n">
+        <v>2.855514341711185</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3.751825439115997</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/Random Forest/predictions_ele.xlsx
+++ b/notebooks/Random Forest/predictions_ele.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_реальный</t>
+          <t>ОПЖ</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -470,16 +470,16 @@
         <v>2023</v>
       </c>
       <c r="C2" t="n">
-        <v>69.17232314228117</v>
+        <v>69.17232314228119</v>
       </c>
       <c r="D2" t="n">
         <v>70.77</v>
       </c>
       <c r="E2" t="n">
-        <v>1.597676857718824</v>
+        <v>1.59767685771881</v>
       </c>
       <c r="F2" t="n">
-        <v>2.257562325446975</v>
+        <v>2.257562325446955</v>
       </c>
     </row>
     <row r="3">
@@ -514,16 +514,16 @@
         <v>2023</v>
       </c>
       <c r="C4" t="n">
-        <v>69.96289246693608</v>
+        <v>69.96289246693607</v>
       </c>
       <c r="D4" t="n">
         <v>71.51000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.547107533063922</v>
+        <v>1.547107533063937</v>
       </c>
       <c r="F4" t="n">
-        <v>2.163484174330754</v>
+        <v>2.163484174330774</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>70.96531310372275</v>
+        <v>70.96531310372274</v>
       </c>
       <c r="D5" t="n">
         <v>72.2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.234686896277253</v>
+        <v>1.234686896277267</v>
       </c>
       <c r="F5" t="n">
-        <v>1.710092654123619</v>
+        <v>1.710092654123639</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +580,16 @@
         <v>2023</v>
       </c>
       <c r="C7" t="n">
-        <v>70.12599540012437</v>
+        <v>70.12599540012434</v>
       </c>
       <c r="D7" t="n">
         <v>71.98</v>
       </c>
       <c r="E7" t="n">
-        <v>1.854004599875637</v>
+        <v>1.854004599875665</v>
       </c>
       <c r="F7" t="n">
-        <v>2.575721867012555</v>
+        <v>2.575721867012594</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>2023</v>
       </c>
       <c r="C8" t="n">
-        <v>69.87102815611038</v>
+        <v>69.87102815611037</v>
       </c>
       <c r="D8" t="n">
         <v>71.62</v>
       </c>
       <c r="E8" t="n">
-        <v>1.74897184388962</v>
+        <v>1.748971843889635</v>
       </c>
       <c r="F8" t="n">
-        <v>2.442015978622759</v>
+        <v>2.442015978622779</v>
       </c>
     </row>
     <row r="9">
@@ -668,16 +668,16 @@
         <v>2023</v>
       </c>
       <c r="C11" t="n">
-        <v>71.39871919260817</v>
+        <v>71.39871919260818</v>
       </c>
       <c r="D11" t="n">
         <v>72.91</v>
       </c>
       <c r="E11" t="n">
-        <v>1.511280807391827</v>
+        <v>1.511280807391813</v>
       </c>
       <c r="F11" t="n">
-        <v>2.072803192143502</v>
+        <v>2.072803192143482</v>
       </c>
     </row>
     <row r="12">
@@ -712,16 +712,16 @@
         <v>2023</v>
       </c>
       <c r="C13" t="n">
-        <v>71.6683741537459</v>
+        <v>71.66837415374589</v>
       </c>
       <c r="D13" t="n">
         <v>73.55</v>
       </c>
       <c r="E13" t="n">
-        <v>1.881625846254096</v>
+        <v>1.88162584625411</v>
       </c>
       <c r="F13" t="n">
-        <v>2.558294828353632</v>
+        <v>2.558294828353651</v>
       </c>
     </row>
     <row r="14">
@@ -778,16 +778,16 @@
         <v>2023</v>
       </c>
       <c r="C16" t="n">
-        <v>74.07435671621003</v>
+        <v>74.07435671621002</v>
       </c>
       <c r="D16" t="n">
         <v>77.14</v>
       </c>
       <c r="E16" t="n">
-        <v>3.065643283789967</v>
+        <v>3.065643283789981</v>
       </c>
       <c r="F16" t="n">
-        <v>3.974129224513828</v>
+        <v>3.974129224513847</v>
       </c>
     </row>
     <row r="17">
@@ -822,16 +822,16 @@
         <v>2023</v>
       </c>
       <c r="C18" t="n">
-        <v>71.58717492090706</v>
+        <v>71.58717492090703</v>
       </c>
       <c r="D18" t="n">
         <v>73.08</v>
       </c>
       <c r="E18" t="n">
-        <v>1.492825079092938</v>
+        <v>1.492825079092967</v>
       </c>
       <c r="F18" t="n">
-        <v>2.042727256558481</v>
+        <v>2.04272725655852</v>
       </c>
     </row>
     <row r="19">
@@ -866,16 +866,16 @@
         <v>2023</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97054796468383</v>
+        <v>73.9705479646838</v>
       </c>
       <c r="D20" t="n">
         <v>76.25</v>
       </c>
       <c r="E20" t="n">
-        <v>2.279452035316169</v>
+        <v>2.279452035316197</v>
       </c>
       <c r="F20" t="n">
-        <v>2.989445292217926</v>
+        <v>2.989445292217964</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         <v>2023</v>
       </c>
       <c r="C21" t="n">
-        <v>68.85492275014022</v>
+        <v>68.85492275014025</v>
       </c>
       <c r="D21" t="n">
         <v>70.29000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.435077249859788</v>
+        <v>1.435077249859759</v>
       </c>
       <c r="F21" t="n">
-        <v>2.041652084023029</v>
+        <v>2.041652084022989</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         <v>2023</v>
       </c>
       <c r="C22" t="n">
-        <v>70.19277824520144</v>
+        <v>70.19277824520141</v>
       </c>
       <c r="D22" t="n">
         <v>71.98999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>1.797221754798557</v>
+        <v>1.797221754798585</v>
       </c>
       <c r="F22" t="n">
-        <v>2.496488060561962</v>
+        <v>2.496488060562002</v>
       </c>
     </row>
     <row r="23">
@@ -954,16 +954,16 @@
         <v>2023</v>
       </c>
       <c r="C24" t="n">
-        <v>72.03225486386093</v>
+        <v>72.03225486386094</v>
       </c>
       <c r="D24" t="n">
         <v>73.70999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>1.677745136139066</v>
+        <v>1.677745136139052</v>
       </c>
       <c r="F24" t="n">
-        <v>2.276143177505177</v>
+        <v>2.276143177505158</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         <v>2023</v>
       </c>
       <c r="C25" t="n">
-        <v>69.68945542232727</v>
+        <v>69.68945542232726</v>
       </c>
       <c r="D25" t="n">
         <v>71.31999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.630544577672723</v>
+        <v>1.630544577672737</v>
       </c>
       <c r="F25" t="n">
-        <v>2.286237489726196</v>
+        <v>2.286237489726215</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         <v>2023</v>
       </c>
       <c r="C26" t="n">
-        <v>68.98858510400166</v>
+        <v>68.98858510400164</v>
       </c>
       <c r="D26" t="n">
         <v>69.79000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8014148959983487</v>
+        <v>0.8014148959983629</v>
       </c>
       <c r="F26" t="n">
-        <v>1.148323393033885</v>
+        <v>1.148323393033906</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         <v>2023</v>
       </c>
       <c r="C27" t="n">
-        <v>70.44914945844457</v>
+        <v>70.44914945844454</v>
       </c>
       <c r="D27" t="n">
         <v>72.45</v>
       </c>
       <c r="E27" t="n">
-        <v>2.000850541555437</v>
+        <v>2.000850541555465</v>
       </c>
       <c r="F27" t="n">
-        <v>2.761698470055813</v>
+        <v>2.761698470055852</v>
       </c>
     </row>
     <row r="28">
@@ -1064,16 +1064,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>71.00473513084108</v>
+        <v>71.00473513084107</v>
       </c>
       <c r="D29" t="n">
         <v>72.44</v>
       </c>
       <c r="E29" t="n">
-        <v>1.435264869158914</v>
+        <v>1.435264869158928</v>
       </c>
       <c r="F29" t="n">
-        <v>1.981315390887512</v>
+        <v>1.981315390887532</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>67.95405593975467</v>
+        <v>67.9540559397547</v>
       </c>
       <c r="D30" t="n">
         <v>69.3</v>
       </c>
       <c r="E30" t="n">
-        <v>1.34594406024533</v>
+        <v>1.345944060245301</v>
       </c>
       <c r="F30" t="n">
-        <v>1.942199221133232</v>
+        <v>1.942199221133191</v>
       </c>
     </row>
     <row r="31">
@@ -1174,16 +1174,16 @@
         <v>2023</v>
       </c>
       <c r="C34" t="n">
-        <v>70.56750871931354</v>
+        <v>70.56750871931352</v>
       </c>
       <c r="D34" t="n">
         <v>72.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.532491280686457</v>
+        <v>1.532491280686472</v>
       </c>
       <c r="F34" t="n">
-        <v>2.125508017595641</v>
+        <v>2.125508017595661</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         <v>2023</v>
       </c>
       <c r="C35" t="n">
-        <v>69.37082216205218</v>
+        <v>69.37082216205216</v>
       </c>
       <c r="D35" t="n">
         <v>70.43000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>1.059177837947828</v>
+        <v>1.059177837947843</v>
       </c>
       <c r="F35" t="n">
-        <v>1.503873119335267</v>
+        <v>1.503873119335287</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         <v>2023</v>
       </c>
       <c r="C36" t="n">
-        <v>70.63271741794561</v>
+        <v>70.63271741794563</v>
       </c>
       <c r="D36" t="n">
         <v>72.2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.567282582054389</v>
+        <v>1.567282582054375</v>
       </c>
       <c r="F36" t="n">
-        <v>2.17075149869029</v>
+        <v>2.17075149869027</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         <v>2023</v>
       </c>
       <c r="C37" t="n">
-        <v>70.62667419691363</v>
+        <v>70.62667419691361</v>
       </c>
       <c r="D37" t="n">
         <v>71.83</v>
       </c>
       <c r="E37" t="n">
-        <v>1.203325803086372</v>
+        <v>1.203325803086386</v>
       </c>
       <c r="F37" t="n">
-        <v>1.675241268392555</v>
+        <v>1.675241268392574</v>
       </c>
     </row>
     <row r="38">
@@ -1284,16 +1284,16 @@
         <v>2023</v>
       </c>
       <c r="C39" t="n">
-        <v>69.81433937512183</v>
+        <v>69.8143393751218</v>
       </c>
       <c r="D39" t="n">
         <v>71.65000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>1.835660624878173</v>
+        <v>1.835660624878201</v>
       </c>
       <c r="F39" t="n">
-        <v>2.56198272837149</v>
+        <v>2.56198272837153</v>
       </c>
     </row>
     <row r="40">
@@ -1306,16 +1306,16 @@
         <v>2023</v>
       </c>
       <c r="C40" t="n">
-        <v>70.9657091239547</v>
+        <v>70.96570912395468</v>
       </c>
       <c r="D40" t="n">
         <v>72.63</v>
       </c>
       <c r="E40" t="n">
-        <v>1.6642908760453</v>
+        <v>1.664290876045314</v>
       </c>
       <c r="F40" t="n">
-        <v>2.291464788717196</v>
+        <v>2.291464788717216</v>
       </c>
     </row>
     <row r="41">
@@ -1350,16 +1350,16 @@
         <v>2023</v>
       </c>
       <c r="C42" t="n">
-        <v>68.86773337070231</v>
+        <v>68.86773337070233</v>
       </c>
       <c r="D42" t="n">
         <v>70.06</v>
       </c>
       <c r="E42" t="n">
-        <v>1.192266629297691</v>
+        <v>1.192266629297677</v>
       </c>
       <c r="F42" t="n">
-        <v>1.701779373819142</v>
+        <v>1.701779373819122</v>
       </c>
     </row>
     <row r="43">
@@ -1394,16 +1394,16 @@
         <v>2023</v>
       </c>
       <c r="C44" t="n">
-        <v>72.62463454567525</v>
+        <v>72.62463454567528</v>
       </c>
       <c r="D44" t="n">
         <v>75.36</v>
       </c>
       <c r="E44" t="n">
-        <v>2.73536545432475</v>
+        <v>2.735365454324722</v>
       </c>
       <c r="F44" t="n">
-        <v>3.629731229199509</v>
+        <v>3.629731229199471</v>
       </c>
     </row>
     <row r="45">
@@ -1416,16 +1416,16 @@
         <v>2023</v>
       </c>
       <c r="C45" t="n">
-        <v>67.95536009920632</v>
+        <v>67.95536009920633</v>
       </c>
       <c r="D45" t="n">
         <v>69.39</v>
       </c>
       <c r="E45" t="n">
-        <v>1.434639900793684</v>
+        <v>1.43463990079367</v>
       </c>
       <c r="F45" t="n">
-        <v>2.067502379008047</v>
+        <v>2.067502379008026</v>
       </c>
     </row>
     <row r="46">
@@ -1438,16 +1438,16 @@
         <v>2023</v>
       </c>
       <c r="C46" t="n">
-        <v>71.89987128651828</v>
+        <v>71.89987128651826</v>
       </c>
       <c r="D46" t="n">
         <v>73.17</v>
       </c>
       <c r="E46" t="n">
-        <v>1.270128713481725</v>
+        <v>1.270128713481739</v>
       </c>
       <c r="F46" t="n">
-        <v>1.735859933691028</v>
+        <v>1.735859933691047</v>
       </c>
     </row>
     <row r="47">
@@ -1460,16 +1460,16 @@
         <v>2023</v>
       </c>
       <c r="C47" t="n">
-        <v>68.73233173425282</v>
+        <v>68.73233173425285</v>
       </c>
       <c r="D47" t="n">
         <v>69.54000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8076682657471821</v>
+        <v>0.8076682657471537</v>
       </c>
       <c r="F47" t="n">
-        <v>1.161444155517949</v>
+        <v>1.161444155517908</v>
       </c>
     </row>
     <row r="48">
@@ -1504,16 +1504,16 @@
         <v>2023</v>
       </c>
       <c r="C49" t="n">
-        <v>76.08253135642138</v>
+        <v>76.08253135642137</v>
       </c>
       <c r="D49" t="n">
         <v>79.2</v>
       </c>
       <c r="E49" t="n">
-        <v>3.117468643578619</v>
+        <v>3.117468643578633</v>
       </c>
       <c r="F49" t="n">
-        <v>3.936197782296235</v>
+        <v>3.936197782296253</v>
       </c>
     </row>
     <row r="50">
@@ -1570,16 +1570,16 @@
         <v>2023</v>
       </c>
       <c r="C52" t="n">
-        <v>69.08796616692338</v>
+        <v>69.08796616692337</v>
       </c>
       <c r="D52" t="n">
         <v>70.43000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>1.342033833076627</v>
+        <v>1.342033833076641</v>
       </c>
       <c r="F52" t="n">
-        <v>1.905486061446297</v>
+        <v>1.905486061446317</v>
       </c>
     </row>
     <row r="53">
@@ -1592,16 +1592,16 @@
         <v>2023</v>
       </c>
       <c r="C53" t="n">
-        <v>71.10719152568714</v>
+        <v>71.10719152568713</v>
       </c>
       <c r="D53" t="n">
         <v>72.76000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>1.652808474312863</v>
+        <v>1.652808474312877</v>
       </c>
       <c r="F53" t="n">
-        <v>2.271589436933566</v>
+        <v>2.271589436933586</v>
       </c>
     </row>
     <row r="54">
@@ -1614,16 +1614,16 @@
         <v>2023</v>
       </c>
       <c r="C54" t="n">
-        <v>71.04943585292639</v>
+        <v>71.04943585292641</v>
       </c>
       <c r="D54" t="n">
         <v>72.04000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9905641470736128</v>
+        <v>0.9905641470735986</v>
       </c>
       <c r="F54" t="n">
-        <v>1.37501963780346</v>
+        <v>1.37501963780344</v>
       </c>
     </row>
     <row r="55">
@@ -1680,16 +1680,16 @@
         <v>2023</v>
       </c>
       <c r="C57" t="n">
-        <v>73.40096261211971</v>
+        <v>73.4009626121197</v>
       </c>
       <c r="D57" t="n">
         <v>76.16</v>
       </c>
       <c r="E57" t="n">
-        <v>2.759037387880284</v>
+        <v>2.759037387880298</v>
       </c>
       <c r="F57" t="n">
-        <v>3.622685645851213</v>
+        <v>3.622685645851231</v>
       </c>
     </row>
     <row r="58">
@@ -1702,16 +1702,16 @@
         <v>2023</v>
       </c>
       <c r="C58" t="n">
-        <v>73.50760974293381</v>
+        <v>73.50760974293379</v>
       </c>
       <c r="D58" t="n">
         <v>75.25</v>
       </c>
       <c r="E58" t="n">
-        <v>1.742390257066191</v>
+        <v>1.742390257066205</v>
       </c>
       <c r="F58" t="n">
-        <v>2.315468780154406</v>
+        <v>2.315468780154426</v>
       </c>
     </row>
     <row r="59">
@@ -1768,16 +1768,16 @@
         <v>2023</v>
       </c>
       <c r="C61" t="n">
-        <v>71.11260269390412</v>
+        <v>71.11260269390409</v>
       </c>
       <c r="D61" t="n">
         <v>73.48</v>
       </c>
       <c r="E61" t="n">
-        <v>2.367397306095882</v>
+        <v>2.36739730609591</v>
       </c>
       <c r="F61" t="n">
-        <v>3.221825402961188</v>
+        <v>3.221825402961227</v>
       </c>
     </row>
     <row r="62">
@@ -1790,16 +1790,16 @@
         <v>2023</v>
       </c>
       <c r="C62" t="n">
-        <v>70.83454384635556</v>
+        <v>70.83454384635553</v>
       </c>
       <c r="D62" t="n">
         <v>73.19</v>
       </c>
       <c r="E62" t="n">
-        <v>2.35545615364444</v>
+        <v>2.355456153644468</v>
       </c>
       <c r="F62" t="n">
-        <v>3.218275930652329</v>
+        <v>3.218275930652368</v>
       </c>
     </row>
     <row r="63">
@@ -1834,16 +1834,16 @@
         <v>2023</v>
       </c>
       <c r="C64" t="n">
-        <v>71.58789735668948</v>
+        <v>71.58789735668947</v>
       </c>
       <c r="D64" t="n">
         <v>73.27</v>
       </c>
       <c r="E64" t="n">
-        <v>1.682102643310515</v>
+        <v>1.682102643310529</v>
       </c>
       <c r="F64" t="n">
-        <v>2.295759032769912</v>
+        <v>2.295759032769932</v>
       </c>
     </row>
     <row r="65">
@@ -1878,16 +1878,16 @@
         <v>2023</v>
       </c>
       <c r="C66" t="n">
-        <v>70.4249294369823</v>
+        <v>70.42492943698227</v>
       </c>
       <c r="D66" t="n">
         <v>71.84</v>
       </c>
       <c r="E66" t="n">
-        <v>1.415070563017707</v>
+        <v>1.415070563017736</v>
       </c>
       <c r="F66" t="n">
-        <v>1.969753010882109</v>
+        <v>1.969753010882148</v>
       </c>
     </row>
     <row r="67">
@@ -1900,16 +1900,16 @@
         <v>2023</v>
       </c>
       <c r="C67" t="n">
-        <v>69.34808430964475</v>
+        <v>69.34808430964476</v>
       </c>
       <c r="D67" t="n">
         <v>71.47</v>
       </c>
       <c r="E67" t="n">
-        <v>2.121915690355252</v>
+        <v>2.121915690355237</v>
       </c>
       <c r="F67" t="n">
-        <v>2.968959969714918</v>
+        <v>2.968959969714898</v>
       </c>
     </row>
     <row r="68">
@@ -1922,16 +1922,16 @@
         <v>2023</v>
       </c>
       <c r="C68" t="n">
-        <v>73.09614713172181</v>
+        <v>73.09614713172182</v>
       </c>
       <c r="D68" t="n">
         <v>74.86</v>
       </c>
       <c r="E68" t="n">
-        <v>1.763852868278192</v>
+        <v>1.763852868278178</v>
       </c>
       <c r="F68" t="n">
-        <v>2.356202068231622</v>
+        <v>2.356202068231603</v>
       </c>
     </row>
     <row r="69">
@@ -1988,16 +1988,16 @@
         <v>2023</v>
       </c>
       <c r="C71" t="n">
-        <v>71.50300814140732</v>
+        <v>71.50300814140731</v>
       </c>
       <c r="D71" t="n">
         <v>73.05</v>
       </c>
       <c r="E71" t="n">
-        <v>1.546991858592676</v>
+        <v>1.546991858592691</v>
       </c>
       <c r="F71" t="n">
-        <v>2.117716438867455</v>
+        <v>2.117716438867475</v>
       </c>
     </row>
     <row r="72">
@@ -2098,16 +2098,16 @@
         <v>2023</v>
       </c>
       <c r="C76" t="n">
-        <v>69.15053701492062</v>
+        <v>69.15053701492063</v>
       </c>
       <c r="D76" t="n">
         <v>70.33</v>
       </c>
       <c r="E76" t="n">
-        <v>1.179462985079383</v>
+        <v>1.179462985079368</v>
       </c>
       <c r="F76" t="n">
-        <v>1.677041070779728</v>
+        <v>1.677041070779708</v>
       </c>
     </row>
     <row r="77">
@@ -2186,16 +2186,16 @@
         <v>2023</v>
       </c>
       <c r="C80" t="n">
-        <v>71.64750904749665</v>
+        <v>71.64750904749664</v>
       </c>
       <c r="D80" t="n">
         <v>73.06999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>1.422490952503338</v>
+        <v>1.422490952503352</v>
       </c>
       <c r="F80" t="n">
-        <v>1.946750995625206</v>
+        <v>1.946750995625226</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>65.4086848881674</v>
+        <v>65.40868488816743</v>
       </c>
       <c r="D81" t="n">
         <v>66.56</v>
       </c>
       <c r="E81" t="n">
-        <v>1.151315111832602</v>
+        <v>1.151315111832574</v>
       </c>
       <c r="F81" t="n">
-        <v>1.729740252152347</v>
+        <v>1.729740252152304</v>
       </c>
     </row>
     <row r="82">
@@ -2274,16 +2274,16 @@
         <v>2023</v>
       </c>
       <c r="C84" t="n">
-        <v>75.76468267857145</v>
+        <v>75.76468267857143</v>
       </c>
       <c r="D84" t="n">
         <v>79.38</v>
       </c>
       <c r="E84" t="n">
-        <v>3.615317321428549</v>
+        <v>3.615317321428563</v>
       </c>
       <c r="F84" t="n">
-        <v>4.554443589605127</v>
+        <v>4.554443589605143</v>
       </c>
     </row>
     <row r="85">
@@ -2296,16 +2296,16 @@
         <v>2023</v>
       </c>
       <c r="C85" t="n">
-        <v>74.46910123588158</v>
+        <v>74.46910123588157</v>
       </c>
       <c r="D85" t="n">
         <v>76.55</v>
       </c>
       <c r="E85" t="n">
-        <v>2.080898764118416</v>
+        <v>2.08089876411843</v>
       </c>
       <c r="F85" t="n">
-        <v>2.718352402506095</v>
+        <v>2.718352402506114</v>
       </c>
     </row>
     <row r="86">
@@ -2318,16 +2318,16 @@
         <v>2023</v>
       </c>
       <c r="C86" t="n">
-        <v>73.25448565828881</v>
+        <v>73.2544856582888</v>
       </c>
       <c r="D86" t="n">
         <v>76.11</v>
       </c>
       <c r="E86" t="n">
-        <v>2.855514341711185</v>
+        <v>2.855514341711199</v>
       </c>
       <c r="F86" t="n">
-        <v>3.751825439115997</v>
+        <v>3.751825439116015</v>
       </c>
     </row>
   </sheetData>
